--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0002T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0002T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.34191627318407</v>
+        <v>2.005561394392411</v>
       </c>
       <c r="D2" t="n">
-        <v>12.78202808059917</v>
+        <v>2.077079563097365</v>
       </c>
       <c r="E2" t="n">
-        <v>10.05258419255167</v>
+        <v>1.633544931289646</v>
       </c>
       <c r="F2" t="n">
-        <v>9.918205605290231</v>
+        <v>1.611708410859663</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.45632229099363</v>
+        <v>5.274152372286465</v>
       </c>
       <c r="D3" t="n">
-        <v>34.46356362627415</v>
+        <v>5.600329089269549</v>
       </c>
       <c r="E3" t="n">
-        <v>10.05258419255167</v>
+        <v>1.633544931289646</v>
       </c>
       <c r="F3" t="n">
-        <v>9.918205605290231</v>
+        <v>1.611708410859663</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>2.692582403567252</v>
+        <v>0.4375446405796785</v>
       </c>
       <c r="D4" t="n">
-        <v>3.905124837953327</v>
+        <v>0.6345827861674157</v>
       </c>
       <c r="E4" t="n">
-        <v>10.05258419255167</v>
+        <v>1.633544931289646</v>
       </c>
       <c r="F4" t="n">
-        <v>9.918205605290231</v>
+        <v>1.611708410859663</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.05848046491341</v>
+        <v>4.39700307554843</v>
       </c>
       <c r="D5" t="n">
-        <v>26.40918031359355</v>
+        <v>4.291491800958952</v>
       </c>
       <c r="E5" t="n">
-        <v>10.05258419255167</v>
+        <v>1.633544931289646</v>
       </c>
       <c r="F5" t="n">
-        <v>9.918205605290231</v>
+        <v>1.611708410859663</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.94013949390892</v>
+        <v>3.7277726677602</v>
       </c>
       <c r="D6" t="n">
-        <v>14.83426963337109</v>
+        <v>2.410568815422802</v>
       </c>
       <c r="E6" t="n">
-        <v>10.05258419255167</v>
+        <v>1.633544931289646</v>
       </c>
       <c r="F6" t="n">
-        <v>9.918205605290231</v>
+        <v>1.611708410859663</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.62559093028396</v>
+        <v>4.001658526171144</v>
       </c>
       <c r="D7" t="n">
-        <v>22.82255651661561</v>
+        <v>3.708665433950037</v>
       </c>
       <c r="E7" t="n">
-        <v>10.05258419255167</v>
+        <v>1.633544931289646</v>
       </c>
       <c r="F7" t="n">
-        <v>9.918205605290231</v>
+        <v>1.611708410859663</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.773948229731499</v>
+        <v>1.425766587331369</v>
       </c>
       <c r="D8" t="n">
-        <v>8.601007067592038</v>
+        <v>1.397663648483706</v>
       </c>
       <c r="E8" t="n">
-        <v>10.05258419255167</v>
+        <v>1.633544931289646</v>
       </c>
       <c r="F8" t="n">
-        <v>9.918205605290231</v>
+        <v>1.611708410859663</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
